--- a/信息收集模板/01-项目信息表.xlsx
+++ b/信息收集模板/01-项目信息表.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填报表" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目信息" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目资料" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -206,79 +207,149 @@
         <t>唯一，字母+数字，如 P1</t>
       </text>
     </comment>
+    <comment ref="C3" authorId="0" shapeId="0">
+      <text>
+        <t>列表卡片显示，建议 20 字以内；不填则显示完整名称</t>
+      </text>
+    </comment>
+    <comment ref="E3" authorId="0" shapeId="0">
+      <text>
+        <t>多人用逗号分隔，如 张三,李四</t>
+      </text>
+    </comment>
+    <comment ref="F3" authorId="0" shapeId="0">
+      <text>
+        <t>如 国家自然科学基金面上项目</t>
+      </text>
+    </comment>
+    <comment ref="G3" authorId="0" shapeId="0">
+      <text>
+        <t>如 NSFC-32171800</t>
+      </text>
+    </comment>
+    <comment ref="H3" authorId="0" shapeId="0">
+      <text>
+        <t>如 NSFC-32171800-01，用于报账/经费管理</t>
+      </text>
+    </comment>
+    <comment ref="I3" authorId="0" shapeId="0">
+      <text>
+        <t>该项目专属飞书云盘文件夹，不填则使用 config.js 全局文件夹</t>
+      </text>
+    </comment>
+    <comment ref="J3" authorId="0" shapeId="0">
+      <text>
+        <t>年-月，如 2022-01</t>
+      </text>
+    </comment>
+    <comment ref="K3" authorId="0" shapeId="0">
+      <text>
+        <t>年-月，如 2025-12</t>
+      </text>
+    </comment>
+    <comment ref="L3" authorId="0" shapeId="0">
+      <text>
+        <t>如 60 万元</t>
+      </text>
+    </comment>
+    <comment ref="M3" authorId="0" shapeId="0">
+      <text>
+        <t>见下拉</t>
+      </text>
+    </comment>
+    <comment ref="N3" authorId="0" shapeId="0">
+      <text>
+        <t>如 基因功能验证</t>
+      </text>
+    </comment>
+    <comment ref="O3" authorId="0" shapeId="0">
+      <text>
+        <t>数字 0-100</t>
+      </text>
+    </comment>
+    <comment ref="P3" authorId="0" shapeId="0">
+      <text>
+        <t>是/否；「是」会在列表显示必读徽章，详情页置顶</t>
+      </text>
+    </comment>
+    <comment ref="R3" authorId="0" shapeId="0">
+      <text>
+        <t>每条一行，可多行</t>
+      </text>
+    </comment>
+    <comment ref="V3" authorId="0" shapeId="0">
+      <text>
+        <t>实验室设备、田间/温室场地、关键材料等</t>
+      </text>
+    </comment>
+    <comment ref="W3" authorId="0" shapeId="0">
+      <text>
+        <t>小区设计、处理梯度、重复数、测定指标等</t>
+      </text>
+    </comment>
+    <comment ref="X3" authorId="0" shapeId="0">
+      <text>
+        <t>如 M1,M2</t>
+      </text>
+    </comment>
+    <comment ref="Y3" authorId="0" shapeId="0">
+      <text>
+        <t>如 S1,S2</t>
+      </text>
+    </comment>
+    <comment ref="Z3" authorId="0" shapeId="0">
+      <text>
+        <t>如 D1</t>
+      </text>
+    </comment>
+    <comment ref="AA3" authorId="0" shapeId="0">
+      <text>
+        <t>如 E1</t>
+      </text>
+    </comment>
+    <comment ref="AB3" authorId="0" shapeId="0">
+      <text>
+        <t>如 A1</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>模板</author>
+  </authors>
+  <commentList>
+    <comment ref="A3" authorId="0" shapeId="0">
+      <text>
+        <t>如 P1</t>
+      </text>
+    </comment>
+    <comment ref="C3" authorId="0" shapeId="0">
+      <text>
+        <t>见下拉：申报立项 / 年度报告 / 中期考核 / 结题验收 / 技术/进展报告 / 经费财务 / 实验资料</t>
+      </text>
+    </comment>
     <comment ref="D3" authorId="0" shapeId="0">
       <text>
-        <t>多人用逗号分隔，如 张三,李四</t>
+        <t>如 PDF / PPT / DOCX / 文件夹</t>
       </text>
     </comment>
     <comment ref="E3" authorId="0" shapeId="0">
       <text>
-        <t>如 国家自然科学基金面上项目</t>
-      </text>
-    </comment>
-    <comment ref="F3" authorId="0" shapeId="0">
-      <text>
-        <t>如 NSFC-32171800</t>
+        <t>年-月，如 2024-12</t>
       </text>
     </comment>
     <comment ref="G3" authorId="0" shapeId="0">
       <text>
-        <t>年-月，如 2022-01</t>
+        <t>飞书云盘分享链接</t>
       </text>
     </comment>
     <comment ref="H3" authorId="0" shapeId="0">
       <text>
-        <t>年-月，如 2025-12</t>
-      </text>
-    </comment>
-    <comment ref="I3" authorId="0" shapeId="0">
-      <text>
-        <t>如 60 万元</t>
-      </text>
-    </comment>
-    <comment ref="J3" authorId="0" shapeId="0">
-      <text>
-        <t>见下拉</t>
-      </text>
-    </comment>
-    <comment ref="K3" authorId="0" shapeId="0">
-      <text>
-        <t>如 基因功能验证</t>
-      </text>
-    </comment>
-    <comment ref="L3" authorId="0" shapeId="0">
-      <text>
-        <t>数字 0-100</t>
-      </text>
-    </comment>
-    <comment ref="N3" authorId="0" shapeId="0">
-      <text>
-        <t>每条一行，可多行</t>
-      </text>
-    </comment>
-    <comment ref="R3" authorId="0" shapeId="0">
-      <text>
-        <t>如 M1,M2</t>
-      </text>
-    </comment>
-    <comment ref="S3" authorId="0" shapeId="0">
-      <text>
-        <t>如 S1,S2</t>
-      </text>
-    </comment>
-    <comment ref="T3" authorId="0" shapeId="0">
-      <text>
-        <t>如 D1</t>
-      </text>
-    </comment>
-    <comment ref="U3" authorId="0" shapeId="0">
-      <text>
-        <t>如 E1</t>
-      </text>
-    </comment>
-    <comment ref="V3" authorId="0" shapeId="0">
-      <text>
-        <t>如 A1</t>
+        <t>是/否；「是」会显示在项目详情页顶部必读区</t>
       </text>
     </comment>
   </commentList>
@@ -574,31 +645,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V19"/>
+  <dimension ref="A1:AB19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="24" customWidth="1" min="14" max="14"/>
-    <col width="16" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="12" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
+    <col width="24" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
     <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="27" max="27"/>
+    <col width="12" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -628,100 +705,130 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>项目简称</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
           <t>项目负责人</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>参与成员</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>项目来源</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>项目外部编号</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>财务编号</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>项目飞书文件夹链接</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>起始时间</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>结束时间</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>经费</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="M3" s="3" t="inlineStr">
         <is>
           <t>当前状态</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="N3" s="3" t="inlineStr">
         <is>
           <t>当前阶段</t>
         </is>
       </c>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="O3" s="3" t="inlineStr">
         <is>
           <t>进度百分比</t>
         </is>
       </c>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>是否必读</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr">
         <is>
           <t>项目目标</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr">
+      <c r="R3" s="3" t="inlineStr">
         <is>
           <t>OKR</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
+      <c r="S3" s="3" t="inlineStr">
         <is>
           <t>本月进展</t>
         </is>
       </c>
-      <c r="P3" s="3" t="inlineStr">
+      <c r="T3" s="3" t="inlineStr">
         <is>
           <t>下一步计划</t>
         </is>
       </c>
-      <c r="Q3" s="3" t="inlineStr">
+      <c r="U3" s="3" t="inlineStr">
         <is>
           <t>风险和问题</t>
         </is>
       </c>
-      <c r="R3" s="3" t="inlineStr">
+      <c r="V3" s="3" t="inlineStr">
+        <is>
+          <t>实验初始设置</t>
+        </is>
+      </c>
+      <c r="W3" s="3" t="inlineStr">
+        <is>
+          <t>实验布置细节</t>
+        </is>
+      </c>
+      <c r="X3" s="3" t="inlineStr">
         <is>
           <t>关联实验方法ID</t>
         </is>
       </c>
-      <c r="S3" s="3" t="inlineStr">
+      <c r="Y3" s="3" t="inlineStr">
         <is>
           <t>关联样品ID</t>
         </is>
       </c>
-      <c r="T3" s="3" t="inlineStr">
+      <c r="Z3" s="3" t="inlineStr">
         <is>
           <t>关联数据ID</t>
         </is>
       </c>
-      <c r="U3" s="3" t="inlineStr">
+      <c r="AA3" s="3" t="inlineStr">
         <is>
           <t>关联报账ID</t>
         </is>
       </c>
-      <c r="V3" s="3" t="inlineStr">
+      <c r="AB3" s="3" t="inlineStr">
         <is>
           <t>关联成果ID</t>
         </is>
@@ -740,98 +847,128 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
+          <t>小麦抗旱基因挖掘</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
           <t>张明远 教授</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>张明远,李文,赵磊,陈思</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>国家自然科学基金面上项目</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>NSFC-32171800</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>NSFC-32171800-01</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>https://my.feishu.cn/drive/folder/xxx</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>2022-01</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="K4" s="4" t="inlineStr">
         <is>
           <t>2025-12</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="L4" s="4" t="inlineStr">
         <is>
           <t>60 万元</t>
         </is>
       </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="M4" s="4" t="inlineStr">
         <is>
           <t>进行中</t>
         </is>
       </c>
-      <c r="K4" s="4" t="inlineStr">
+      <c r="N4" s="4" t="inlineStr">
         <is>
           <t>基因功能验证</t>
         </is>
       </c>
-      <c r="L4" s="4" t="n">
+      <c r="O4" s="4" t="n">
         <v>72</v>
       </c>
-      <c r="M4" s="4" t="inlineStr">
+      <c r="P4" s="4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Q4" s="4" t="inlineStr">
         <is>
           <t>挖掘 2–3 个抗旱主效基因</t>
         </is>
       </c>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="R4" s="4" t="inlineStr">
         <is>
           <t>O：完成抗旱资源筛选 KR：鉴定50份抗旱种质</t>
         </is>
       </c>
-      <c r="O4" s="4" t="inlineStr">
+      <c r="S4" s="4" t="inlineStr">
         <is>
           <t>本月完成转录组第3批取样</t>
         </is>
       </c>
-      <c r="P4" s="4" t="inlineStr">
+      <c r="T4" s="4" t="inlineStr">
         <is>
           <t>下月开展VIGS验证</t>
         </is>
       </c>
-      <c r="Q4" s="4" t="inlineStr">
+      <c r="U4" s="4" t="inlineStr">
         <is>
           <t>转基因材料构建周期长</t>
         </is>
       </c>
-      <c r="R4" s="4" t="inlineStr">
+      <c r="V4" s="4" t="inlineStr">
+        <is>
+          <t>待补充</t>
+        </is>
+      </c>
+      <c r="W4" s="4" t="inlineStr">
+        <is>
+          <t>待补充</t>
+        </is>
+      </c>
+      <c r="X4" s="4" t="inlineStr">
         <is>
           <t>M1,M2,M5</t>
         </is>
       </c>
-      <c r="S4" s="4" t="inlineStr">
+      <c r="Y4" s="4" t="inlineStr">
         <is>
           <t>S1,S2,S3</t>
         </is>
       </c>
-      <c r="T4" s="4" t="inlineStr">
+      <c r="Z4" s="4" t="inlineStr">
         <is>
           <t>D1,D2</t>
         </is>
       </c>
-      <c r="U4" s="4" t="inlineStr">
+      <c r="AA4" s="4" t="inlineStr">
         <is>
           <t>E1,E2</t>
         </is>
       </c>
-      <c r="V4" s="4" t="inlineStr">
+      <c r="AB4" s="4" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
@@ -860,6 +997,12 @@
       <c r="T5" s="5" t="n"/>
       <c r="U5" s="5" t="n"/>
       <c r="V5" s="5" t="n"/>
+      <c r="W5" s="5" t="n"/>
+      <c r="X5" s="5" t="n"/>
+      <c r="Y5" s="5" t="n"/>
+      <c r="Z5" s="5" t="n"/>
+      <c r="AA5" s="5" t="n"/>
+      <c r="AB5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="n"/>
@@ -884,6 +1027,12 @@
       <c r="T6" s="5" t="n"/>
       <c r="U6" s="5" t="n"/>
       <c r="V6" s="5" t="n"/>
+      <c r="W6" s="5" t="n"/>
+      <c r="X6" s="5" t="n"/>
+      <c r="Y6" s="5" t="n"/>
+      <c r="Z6" s="5" t="n"/>
+      <c r="AA6" s="5" t="n"/>
+      <c r="AB6" s="5" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
@@ -908,6 +1057,12 @@
       <c r="T7" s="5" t="n"/>
       <c r="U7" s="5" t="n"/>
       <c r="V7" s="5" t="n"/>
+      <c r="W7" s="5" t="n"/>
+      <c r="X7" s="5" t="n"/>
+      <c r="Y7" s="5" t="n"/>
+      <c r="Z7" s="5" t="n"/>
+      <c r="AA7" s="5" t="n"/>
+      <c r="AB7" s="5" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
@@ -932,6 +1087,12 @@
       <c r="T8" s="5" t="n"/>
       <c r="U8" s="5" t="n"/>
       <c r="V8" s="5" t="n"/>
+      <c r="W8" s="5" t="n"/>
+      <c r="X8" s="5" t="n"/>
+      <c r="Y8" s="5" t="n"/>
+      <c r="Z8" s="5" t="n"/>
+      <c r="AA8" s="5" t="n"/>
+      <c r="AB8" s="5" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n"/>
@@ -956,6 +1117,12 @@
       <c r="T9" s="5" t="n"/>
       <c r="U9" s="5" t="n"/>
       <c r="V9" s="5" t="n"/>
+      <c r="W9" s="5" t="n"/>
+      <c r="X9" s="5" t="n"/>
+      <c r="Y9" s="5" t="n"/>
+      <c r="Z9" s="5" t="n"/>
+      <c r="AA9" s="5" t="n"/>
+      <c r="AB9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="n"/>
@@ -980,6 +1147,12 @@
       <c r="T10" s="5" t="n"/>
       <c r="U10" s="5" t="n"/>
       <c r="V10" s="5" t="n"/>
+      <c r="W10" s="5" t="n"/>
+      <c r="X10" s="5" t="n"/>
+      <c r="Y10" s="5" t="n"/>
+      <c r="Z10" s="5" t="n"/>
+      <c r="AA10" s="5" t="n"/>
+      <c r="AB10" s="5" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
@@ -1004,6 +1177,12 @@
       <c r="T11" s="5" t="n"/>
       <c r="U11" s="5" t="n"/>
       <c r="V11" s="5" t="n"/>
+      <c r="W11" s="5" t="n"/>
+      <c r="X11" s="5" t="n"/>
+      <c r="Y11" s="5" t="n"/>
+      <c r="Z11" s="5" t="n"/>
+      <c r="AA11" s="5" t="n"/>
+      <c r="AB11" s="5" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
@@ -1028,6 +1207,12 @@
       <c r="T12" s="5" t="n"/>
       <c r="U12" s="5" t="n"/>
       <c r="V12" s="5" t="n"/>
+      <c r="W12" s="5" t="n"/>
+      <c r="X12" s="5" t="n"/>
+      <c r="Y12" s="5" t="n"/>
+      <c r="Z12" s="5" t="n"/>
+      <c r="AA12" s="5" t="n"/>
+      <c r="AB12" s="5" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
@@ -1052,6 +1237,12 @@
       <c r="T13" s="5" t="n"/>
       <c r="U13" s="5" t="n"/>
       <c r="V13" s="5" t="n"/>
+      <c r="W13" s="5" t="n"/>
+      <c r="X13" s="5" t="n"/>
+      <c r="Y13" s="5" t="n"/>
+      <c r="Z13" s="5" t="n"/>
+      <c r="AA13" s="5" t="n"/>
+      <c r="AB13" s="5" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="n"/>
@@ -1076,6 +1267,12 @@
       <c r="T14" s="5" t="n"/>
       <c r="U14" s="5" t="n"/>
       <c r="V14" s="5" t="n"/>
+      <c r="W14" s="5" t="n"/>
+      <c r="X14" s="5" t="n"/>
+      <c r="Y14" s="5" t="n"/>
+      <c r="Z14" s="5" t="n"/>
+      <c r="AA14" s="5" t="n"/>
+      <c r="AB14" s="5" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n"/>
@@ -1100,6 +1297,12 @@
       <c r="T15" s="5" t="n"/>
       <c r="U15" s="5" t="n"/>
       <c r="V15" s="5" t="n"/>
+      <c r="W15" s="5" t="n"/>
+      <c r="X15" s="5" t="n"/>
+      <c r="Y15" s="5" t="n"/>
+      <c r="Z15" s="5" t="n"/>
+      <c r="AA15" s="5" t="n"/>
+      <c r="AB15" s="5" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n"/>
@@ -1124,6 +1327,12 @@
       <c r="T16" s="5" t="n"/>
       <c r="U16" s="5" t="n"/>
       <c r="V16" s="5" t="n"/>
+      <c r="W16" s="5" t="n"/>
+      <c r="X16" s="5" t="n"/>
+      <c r="Y16" s="5" t="n"/>
+      <c r="Z16" s="5" t="n"/>
+      <c r="AA16" s="5" t="n"/>
+      <c r="AB16" s="5" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="n"/>
@@ -1148,6 +1357,12 @@
       <c r="T17" s="5" t="n"/>
       <c r="U17" s="5" t="n"/>
       <c r="V17" s="5" t="n"/>
+      <c r="W17" s="5" t="n"/>
+      <c r="X17" s="5" t="n"/>
+      <c r="Y17" s="5" t="n"/>
+      <c r="Z17" s="5" t="n"/>
+      <c r="AA17" s="5" t="n"/>
+      <c r="AB17" s="5" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="n"/>
@@ -1172,6 +1387,12 @@
       <c r="T18" s="5" t="n"/>
       <c r="U18" s="5" t="n"/>
       <c r="V18" s="5" t="n"/>
+      <c r="W18" s="5" t="n"/>
+      <c r="X18" s="5" t="n"/>
+      <c r="Y18" s="5" t="n"/>
+      <c r="Z18" s="5" t="n"/>
+      <c r="AA18" s="5" t="n"/>
+      <c r="AB18" s="5" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n"/>
@@ -1196,15 +1417,610 @@
       <c r="T19" s="5" t="n"/>
       <c r="U19" s="5" t="n"/>
       <c r="V19" s="5" t="n"/>
+      <c r="W19" s="5" t="n"/>
+      <c r="X19" s="5" t="n"/>
+      <c r="Y19" s="5" t="n"/>
+      <c r="Z19" s="5" t="n"/>
+      <c r="AA19" s="5" t="n"/>
+      <c r="AB19" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:V2"/>
-    <mergeCell ref="A1:V1"/>
+    <mergeCell ref="A2:AB2"/>
+    <mergeCell ref="A1:AB1"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="J5:J19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+  <dataValidations count="2">
+    <dataValidation sqref="M5:M19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"准备中,进行中,暂停,结题中,已结题"</formula1>
+    </dataValidation>
+    <dataValidation sqref="P5:P19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"是,否"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I44"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>项目资料</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>填写说明：每条资料一行；项目编号对应「项目信息」sheet 的项目编号。类别必须从下拉中选择，链接为飞书云盘文件/文件夹分享链接。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>项目编号</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>资料名称</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>类别</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>类型</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>上传人</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>链接</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>是否必读</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="42" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>项目申请书</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>申报立项</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>张明远</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>https://my.feishu.cn/file/xxx</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>终稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="n"/>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="5" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="n"/>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n"/>
+      <c r="I6" s="5" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n"/>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="5" t="n"/>
+      <c r="I7" s="5" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="n"/>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n"/>
+      <c r="I8" s="5" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n"/>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="n"/>
+      <c r="I9" s="5" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="n"/>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="5" t="n"/>
+      <c r="I10" s="5" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n"/>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="5" t="n"/>
+      <c r="I11" s="5" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="n"/>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="5" t="n"/>
+      <c r="I12" s="5" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n"/>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5" t="n"/>
+      <c r="H13" s="5" t="n"/>
+      <c r="I13" s="5" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="n"/>
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="5" t="n"/>
+      <c r="I14" s="5" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n"/>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="5" t="n"/>
+      <c r="I15" s="5" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="n"/>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="5" t="n"/>
+      <c r="H16" s="5" t="n"/>
+      <c r="I16" s="5" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="n"/>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="5" t="n"/>
+      <c r="I17" s="5" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="n"/>
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="5" t="n"/>
+      <c r="H18" s="5" t="n"/>
+      <c r="I18" s="5" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="n"/>
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="5" t="n"/>
+      <c r="H19" s="5" t="n"/>
+      <c r="I19" s="5" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="n"/>
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="5" t="n"/>
+      <c r="I20" s="5" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="n"/>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="5" t="n"/>
+      <c r="H21" s="5" t="n"/>
+      <c r="I21" s="5" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="n"/>
+      <c r="B22" s="5" t="n"/>
+      <c r="C22" s="5" t="n"/>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="5" t="n"/>
+      <c r="I22" s="5" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="n"/>
+      <c r="B23" s="5" t="n"/>
+      <c r="C23" s="5" t="n"/>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="5" t="n"/>
+      <c r="I23" s="5" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="n"/>
+      <c r="B24" s="5" t="n"/>
+      <c r="C24" s="5" t="n"/>
+      <c r="D24" s="5" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="5" t="n"/>
+      <c r="H24" s="5" t="n"/>
+      <c r="I24" s="5" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="n"/>
+      <c r="B25" s="5" t="n"/>
+      <c r="C25" s="5" t="n"/>
+      <c r="D25" s="5" t="n"/>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="5" t="n"/>
+      <c r="H25" s="5" t="n"/>
+      <c r="I25" s="5" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="n"/>
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="5" t="n"/>
+      <c r="D26" s="5" t="n"/>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="5" t="n"/>
+      <c r="G26" s="5" t="n"/>
+      <c r="H26" s="5" t="n"/>
+      <c r="I26" s="5" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="n"/>
+      <c r="B27" s="5" t="n"/>
+      <c r="C27" s="5" t="n"/>
+      <c r="D27" s="5" t="n"/>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="5" t="n"/>
+      <c r="G27" s="5" t="n"/>
+      <c r="H27" s="5" t="n"/>
+      <c r="I27" s="5" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="n"/>
+      <c r="B28" s="5" t="n"/>
+      <c r="C28" s="5" t="n"/>
+      <c r="D28" s="5" t="n"/>
+      <c r="E28" s="5" t="n"/>
+      <c r="F28" s="5" t="n"/>
+      <c r="G28" s="5" t="n"/>
+      <c r="H28" s="5" t="n"/>
+      <c r="I28" s="5" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="n"/>
+      <c r="B29" s="5" t="n"/>
+      <c r="C29" s="5" t="n"/>
+      <c r="D29" s="5" t="n"/>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="5" t="n"/>
+      <c r="G29" s="5" t="n"/>
+      <c r="H29" s="5" t="n"/>
+      <c r="I29" s="5" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="n"/>
+      <c r="B30" s="5" t="n"/>
+      <c r="C30" s="5" t="n"/>
+      <c r="D30" s="5" t="n"/>
+      <c r="E30" s="5" t="n"/>
+      <c r="F30" s="5" t="n"/>
+      <c r="G30" s="5" t="n"/>
+      <c r="H30" s="5" t="n"/>
+      <c r="I30" s="5" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="n"/>
+      <c r="B31" s="5" t="n"/>
+      <c r="C31" s="5" t="n"/>
+      <c r="D31" s="5" t="n"/>
+      <c r="E31" s="5" t="n"/>
+      <c r="F31" s="5" t="n"/>
+      <c r="G31" s="5" t="n"/>
+      <c r="H31" s="5" t="n"/>
+      <c r="I31" s="5" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="n"/>
+      <c r="B32" s="5" t="n"/>
+      <c r="C32" s="5" t="n"/>
+      <c r="D32" s="5" t="n"/>
+      <c r="E32" s="5" t="n"/>
+      <c r="F32" s="5" t="n"/>
+      <c r="G32" s="5" t="n"/>
+      <c r="H32" s="5" t="n"/>
+      <c r="I32" s="5" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="n"/>
+      <c r="B33" s="5" t="n"/>
+      <c r="C33" s="5" t="n"/>
+      <c r="D33" s="5" t="n"/>
+      <c r="E33" s="5" t="n"/>
+      <c r="F33" s="5" t="n"/>
+      <c r="G33" s="5" t="n"/>
+      <c r="H33" s="5" t="n"/>
+      <c r="I33" s="5" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="n"/>
+      <c r="B34" s="5" t="n"/>
+      <c r="C34" s="5" t="n"/>
+      <c r="D34" s="5" t="n"/>
+      <c r="E34" s="5" t="n"/>
+      <c r="F34" s="5" t="n"/>
+      <c r="G34" s="5" t="n"/>
+      <c r="H34" s="5" t="n"/>
+      <c r="I34" s="5" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="n"/>
+      <c r="B35" s="5" t="n"/>
+      <c r="C35" s="5" t="n"/>
+      <c r="D35" s="5" t="n"/>
+      <c r="E35" s="5" t="n"/>
+      <c r="F35" s="5" t="n"/>
+      <c r="G35" s="5" t="n"/>
+      <c r="H35" s="5" t="n"/>
+      <c r="I35" s="5" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="n"/>
+      <c r="B36" s="5" t="n"/>
+      <c r="C36" s="5" t="n"/>
+      <c r="D36" s="5" t="n"/>
+      <c r="E36" s="5" t="n"/>
+      <c r="F36" s="5" t="n"/>
+      <c r="G36" s="5" t="n"/>
+      <c r="H36" s="5" t="n"/>
+      <c r="I36" s="5" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="n"/>
+      <c r="B37" s="5" t="n"/>
+      <c r="C37" s="5" t="n"/>
+      <c r="D37" s="5" t="n"/>
+      <c r="E37" s="5" t="n"/>
+      <c r="F37" s="5" t="n"/>
+      <c r="G37" s="5" t="n"/>
+      <c r="H37" s="5" t="n"/>
+      <c r="I37" s="5" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="n"/>
+      <c r="B38" s="5" t="n"/>
+      <c r="C38" s="5" t="n"/>
+      <c r="D38" s="5" t="n"/>
+      <c r="E38" s="5" t="n"/>
+      <c r="F38" s="5" t="n"/>
+      <c r="G38" s="5" t="n"/>
+      <c r="H38" s="5" t="n"/>
+      <c r="I38" s="5" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="n"/>
+      <c r="B39" s="5" t="n"/>
+      <c r="C39" s="5" t="n"/>
+      <c r="D39" s="5" t="n"/>
+      <c r="E39" s="5" t="n"/>
+      <c r="F39" s="5" t="n"/>
+      <c r="G39" s="5" t="n"/>
+      <c r="H39" s="5" t="n"/>
+      <c r="I39" s="5" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="n"/>
+      <c r="B40" s="5" t="n"/>
+      <c r="C40" s="5" t="n"/>
+      <c r="D40" s="5" t="n"/>
+      <c r="E40" s="5" t="n"/>
+      <c r="F40" s="5" t="n"/>
+      <c r="G40" s="5" t="n"/>
+      <c r="H40" s="5" t="n"/>
+      <c r="I40" s="5" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="n"/>
+      <c r="B41" s="5" t="n"/>
+      <c r="C41" s="5" t="n"/>
+      <c r="D41" s="5" t="n"/>
+      <c r="E41" s="5" t="n"/>
+      <c r="F41" s="5" t="n"/>
+      <c r="G41" s="5" t="n"/>
+      <c r="H41" s="5" t="n"/>
+      <c r="I41" s="5" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="n"/>
+      <c r="B42" s="5" t="n"/>
+      <c r="C42" s="5" t="n"/>
+      <c r="D42" s="5" t="n"/>
+      <c r="E42" s="5" t="n"/>
+      <c r="F42" s="5" t="n"/>
+      <c r="G42" s="5" t="n"/>
+      <c r="H42" s="5" t="n"/>
+      <c r="I42" s="5" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="n"/>
+      <c r="B43" s="5" t="n"/>
+      <c r="C43" s="5" t="n"/>
+      <c r="D43" s="5" t="n"/>
+      <c r="E43" s="5" t="n"/>
+      <c r="F43" s="5" t="n"/>
+      <c r="G43" s="5" t="n"/>
+      <c r="H43" s="5" t="n"/>
+      <c r="I43" s="5" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="n"/>
+      <c r="B44" s="5" t="n"/>
+      <c r="C44" s="5" t="n"/>
+      <c r="D44" s="5" t="n"/>
+      <c r="E44" s="5" t="n"/>
+      <c r="F44" s="5" t="n"/>
+      <c r="G44" s="5" t="n"/>
+      <c r="H44" s="5" t="n"/>
+      <c r="I44" s="5" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation sqref="C5:C44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"申报立项,年度报告,中期考核,结题验收,技术/进展报告,经费财务,实验资料"</formula1>
+    </dataValidation>
+    <dataValidation sqref="H5:H44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"是,否"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
